--- a/out/Attention_Base_repeat_3_000006.xlsx
+++ b/out/Attention_Base_repeat_3_000006.xlsx
@@ -2527,14 +2527,14 @@
       </c>
       <c r="IZ2" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA2" t="n">
         <v>1</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.3</v>
+        <v>0.8053588248051395</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3322,14 +3322,14 @@
       </c>
       <c r="IZ3" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA3" t="n">
         <v>1</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.3</v>
+        <v>0.8053588248051395</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4117,14 +4117,14 @@
       </c>
       <c r="IZ4" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA4" t="n">
         <v>1</v>
       </c>
       <c r="JB4" t="n">
-        <v>-0.3</v>
+        <v>1.40535882480514</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4912,14 +4912,14 @@
       </c>
       <c r="IZ5" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA5" t="n">
         <v>1</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.3</v>
+        <v>1.40535882480514</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5707,14 +5707,14 @@
       </c>
       <c r="IZ6" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA6" t="n">
         <v>1</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.3</v>
+        <v>1.40535882480514</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6502,14 +6502,14 @@
       </c>
       <c r="IZ7" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA7" t="n">
         <v>1</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.3</v>
+        <v>1.40535882480514</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7297,14 +7297,14 @@
       </c>
       <c r="IZ8" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA8" t="n">
         <v>1</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.3</v>
+        <v>1.40535882480514</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8092,14 +8092,14 @@
       </c>
       <c r="IZ9" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA9" t="n">
         <v>1</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.3</v>
+        <v>1.40535882480514</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8887,14 +8887,14 @@
       </c>
       <c r="IZ10" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA10" t="n">
         <v>1</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.3</v>
+        <v>1.40535882480514</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9682,14 +9682,14 @@
       </c>
       <c r="IZ11" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA11" t="n">
         <v>1</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.3</v>
+        <v>0.8053588248051395</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10477,14 +10477,14 @@
       </c>
       <c r="IZ12" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA12" t="n">
         <v>1</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.3</v>
+        <v>0.8053588248051395</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11272,14 +11272,14 @@
       </c>
       <c r="IZ13" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA13" t="n">
         <v>1</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.3</v>
+        <v>0.8053588248051395</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12067,14 +12067,14 @@
       </c>
       <c r="IZ14" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA14" t="n">
         <v>1</v>
       </c>
       <c r="JB14" t="n">
-        <v>-0.3</v>
+        <v>0.8053588248051395</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12862,14 +12862,14 @@
       </c>
       <c r="IZ15" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA15" t="n">
         <v>1</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.3</v>
+        <v>0.8053588248051395</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13661,10 +13661,10 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.3</v>
+        <v>-2.073179781458244</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14456,10 +14456,10 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.3</v>
+        <v>-2.073179781458244</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15251,10 +15251,10 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.3</v>
+        <v>-2.073179781458244</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16046,10 +16046,10 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.3</v>
+        <v>-2.073179781458244</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16841,10 +16841,10 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>-0.3</v>
+        <v>-2.073179781458244</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17636,10 +17636,10 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>-0.3</v>
+        <v>-2.073179781458244</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18431,10 +18431,10 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.3</v>
+        <v>-2.073179781458244</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19226,10 +19226,10 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>-0.3</v>
+        <v>-2.073179781458244</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20021,10 +20021,10 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.3</v>
+        <v>-2.073179781458244</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20816,10 +20816,10 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>-0.3</v>
+        <v>-2.073179781458244</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21611,10 +21611,10 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.3</v>
+        <v>-2.073179781458244</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22406,10 +22406,10 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.3</v>
+        <v>-2.073179781458244</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23197,14 +23197,14 @@
       </c>
       <c r="IZ28" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA28" t="n">
         <v>1</v>
       </c>
       <c r="JB28" t="n">
-        <v>-0.3</v>
+        <v>1.40535882480514</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23992,14 +23992,14 @@
       </c>
       <c r="IZ29" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA29" t="n">
         <v>1</v>
       </c>
       <c r="JB29" t="n">
-        <v>-0.3</v>
+        <v>1.40535882480514</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24787,14 +24787,14 @@
       </c>
       <c r="IZ30" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA30" t="n">
         <v>1</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.3</v>
+        <v>1.40535882480514</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25582,14 +25582,14 @@
       </c>
       <c r="IZ31" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA31" t="n">
         <v>1</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.3</v>
+        <v>1.40535882480514</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26377,14 +26377,14 @@
       </c>
       <c r="IZ32" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA32" t="n">
         <v>1</v>
       </c>
       <c r="JB32" t="n">
-        <v>-0.3</v>
+        <v>1.40535882480514</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27176,10 +27176,10 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.3</v>
+        <v>-1.473179781458244</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27971,10 +27971,10 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.3</v>
+        <v>-2.073179781458244</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28766,10 +28766,10 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>-0.3</v>
+        <v>-2.073179781458244</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29561,10 +29561,10 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>-0.3</v>
+        <v>-2.073179781458244</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30356,10 +30356,10 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>-0.3</v>
+        <v>-2.073179781458244</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31151,10 +31151,10 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB38" t="n">
-        <v>-0.3</v>
+        <v>-2.073179781458244</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31946,10 +31946,10 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>-0.3</v>
+        <v>-2.073179781458244</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32741,10 +32741,10 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB40" t="n">
-        <v>-0.3</v>
+        <v>-2.073179781458244</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33536,10 +33536,10 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB41" t="n">
-        <v>-0.3</v>
+        <v>-2.073179781458244</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34331,10 +34331,10 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB42" t="n">
-        <v>-0.3</v>
+        <v>-2.073179781458244</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35126,10 +35126,10 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB43" t="n">
-        <v>-0.3</v>
+        <v>-2.073179781458244</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35924,10 +35924,10 @@
         <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>-0.3</v>
+        <v>1.40535882480514</v>
       </c>
       <c r="JC44" t="n">
-        <v>-6.556325642217417e-05</v>
+        <v>-0.0002613199841422029</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.08438480768506497</v>
+        <v>0.336339175438052</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36719,10 +36719,10 @@
         <v>1</v>
       </c>
       <c r="JB45" t="n">
-        <v>-0.3</v>
+        <v>1.40535882480514</v>
       </c>
       <c r="JC45" t="n">
-        <v>0.1689297339021736</v>
+        <v>0.6733148663845712</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.0194880177913958</v>
+        <v>-0.07767454023522528</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>1</v>
       </c>
       <c r="JB46" t="n">
-        <v>-0.3</v>
+        <v>1.40535882480514</v>
       </c>
       <c r="JC46" t="n">
-        <v>0.06483122663724702</v>
+        <v>0.2584033152186847</v>
       </c>
     </row>
     <row r="47">
@@ -38309,10 +38309,10 @@
         <v>1</v>
       </c>
       <c r="JB47" t="n">
-        <v>-0.3</v>
+        <v>1.40535882480514</v>
       </c>
       <c r="JC47" t="n">
-        <v>0.06483122663724702</v>
+        <v>0.2584033152186847</v>
       </c>
     </row>
     <row r="48">
@@ -39104,10 +39104,10 @@
         <v>1</v>
       </c>
       <c r="JB48" t="n">
-        <v>-0.3</v>
+        <v>1.40535882480514</v>
       </c>
       <c r="JC48" t="n">
-        <v>0.06475166442322568</v>
+        <v>0.2581284375007423</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.2444321660704994</v>
+        <v>0.8444836348673075</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39899,10 +39899,10 @@
         <v>1</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.3</v>
+        <v>1.40535882480514</v>
       </c>
       <c r="JC49" t="n">
-        <v>0.5541030433219986</v>
+        <v>1.948777596716293</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.0467694028973443</v>
+        <v>0.1615824281827513</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40694,10 +40694,10 @@
         <v>1</v>
       </c>
       <c r="JB50" t="n">
-        <v>-0.3</v>
+        <v>1.40535882480514</v>
       </c>
       <c r="JC50" t="n">
-        <v>0.4028526571241431</v>
+        <v>1.426226258971965</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.08192082715885056</v>
+        <v>0.2830269471308689</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41489,10 +41489,10 @@
         <v>1</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.3</v>
+        <v>1.40535882480514</v>
       </c>
       <c r="JC51" t="n">
-        <v>0.5199482700256048</v>
+        <v>1.830777242861513</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.04486282609988666</v>
+        <v>0.1549960940300547</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42284,10 +42284,10 @@
         <v>1</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.3</v>
+        <v>1.40535882480514</v>
       </c>
       <c r="JC52" t="n">
-        <v>0.527682525776231</v>
+        <v>1.857498096214973</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.01852900052948198</v>
+        <v>0.06401564408707144</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43076,13 +43076,13 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.3</v>
+        <v>-2.073179781458244</v>
       </c>
       <c r="JC53" t="n">
-        <v>0.5198305874830726</v>
+        <v>1.830370806137095</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.02308603502812542</v>
+        <v>0.07975799908004615</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43874,10 +43874,10 @@
         <v>1</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.3</v>
+        <v>0.8053588248051395</v>
       </c>
       <c r="JC54" t="n">
-        <v>0.5474763734630048</v>
+        <v>1.925881904949355</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.01389973439154032</v>
+        <v>0.0480246179756631</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44669,10 +44669,10 @@
         <v>1</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.3</v>
+        <v>0.8053588248051395</v>
       </c>
       <c r="JC55" t="n">
-        <v>0.5521757733858368</v>
+        <v>1.94211901810823</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.01056623891274916</v>
+        <v>0.03651162003562399</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45464,10 +45464,10 @@
         <v>1</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.3</v>
+        <v>1.40535882480514</v>
       </c>
       <c r="JC56" t="n">
-        <v>0.5594043808195763</v>
+        <v>1.967097118697055</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>0.004670697256883739</v>
+        <v>0.01614839016883085</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46259,10 +46259,10 @@
         <v>1</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.3</v>
+        <v>1.40535882480514</v>
       </c>
       <c r="JC57" t="n">
-        <v>0.5581718723189736</v>
+        <v>1.962851666483928</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>0.003705173577296268</v>
+        <v>0.01281288043495556</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47054,10 +47054,10 @@
         <v>1</v>
       </c>
       <c r="JB58" t="n">
-        <v>-0.3</v>
+        <v>1.40535882480514</v>
       </c>
       <c r="JC58" t="n">
-        <v>0.5609111095432001</v>
+        <v>1.972325144222151</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>0.001836089473792515</v>
+        <v>0.006351261349058125</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47849,10 +47849,10 @@
         <v>1</v>
       </c>
       <c r="JB59" t="n">
-        <v>-0.3</v>
+        <v>1.40535882480514</v>
       </c>
       <c r="JC59" t="n">
-        <v>0.5608732506654687</v>
+        <v>1.972206679976134</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.001065585874391671</v>
+        <v>0.003692594147695146</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>1</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.3</v>
+        <v>1.40535882480514</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.561167360520143</v>
+        <v>1.973234746892687</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.0005302929371958355</v>
+        <v>0.001842342473474759</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>1</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.3</v>
+        <v>1.40535882480514</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.5611616940443013</v>
+        <v>1.973227446826601</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.0002594676309391166</v>
+        <v>0.0009091381156373814</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50234,10 +50234,10 @@
         <v>1</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.3</v>
+        <v>1.40535882480514</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.5611499993118744</v>
+        <v>1.97319930633843</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.0001485320277835259</v>
+        <v>0.0005256867916865352</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51029,10 +51029,10 @@
         <v>1</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.3</v>
+        <v>0.8053588248051395</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.5611874566156971</v>
+        <v>1.973341060932079</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>4.633531262135388e-05</v>
+        <v>0.0001713256390037807</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51824,10 +51824,10 @@
         <v>1</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.3</v>
+        <v>0.8053588248051395</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.5611314695106868</v>
+        <v>1.973159824299444</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>1.970370261998147e-05</v>
+        <v>8.483164589084172e-05</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52619,10 +52619,10 @@
         <v>1</v>
       </c>
       <c r="JB65" t="n">
-        <v>-0.3</v>
+        <v>0.8053588248051395</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.5611267567002347</v>
+        <v>1.973155818306387</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>9.677176780651038e-06</v>
+        <v>4.392392260217012e-05</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53414,10 +53414,10 @@
         <v>1</v>
       </c>
       <c r="JB66" t="n">
-        <v>-0.3</v>
+        <v>0.8053588248051395</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.5611241460540584</v>
+        <v>1.973158782819132</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>2.110541340889784e-06</v>
+        <v>1.870180446963262e-05</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54209,10 +54209,10 @@
         <v>1</v>
       </c>
       <c r="JB67" t="n">
-        <v>-0.3</v>
+        <v>0.8053588248051395</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.5611186804883393</v>
+        <v>1.973152230933403</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>-2.090799254370459e-06</v>
+        <v>9.546003728147707e-06</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55004,10 +55004,10 @@
         <v>1</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.3</v>
+        <v>0.8053588248051395</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.5611152958698885</v>
+        <v>1.973152609501648</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>-2.422504053549707e-06</v>
+        <v>1.549918929005845e-07</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55799,10 +55799,10 @@
         <v>1</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.3</v>
+        <v>0.8053588248051395</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.5611096284396148</v>
+        <v>1.973145942537778</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>0</v>
+        <v>-2.042425637823487e-06</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56594,10 +56594,10 @@
         <v>1</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.3</v>
+        <v>0.8053588248051395</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.5611100089746726</v>
+        <v>1.973142080462682</v>
       </c>
     </row>
     <row r="71">
@@ -57378,7 +57378,7 @@
         <v>0</v>
       </c>
       <c r="IY71" t="n">
-        <v>0</v>
+        <v>-1.814378588387752e-06</v>
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
@@ -57389,10 +57389,10 @@
         <v>1</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.3</v>
+        <v>0.8053588248051395</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.5611102372957072</v>
+        <v>1.973137533150496</v>
       </c>
     </row>
     <row r="72">
@@ -58184,10 +58184,10 @@
         <v>1</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.3</v>
+        <v>0.8053588248051395</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.5611103272403571</v>
+        <v>1.973137623095146</v>
       </c>
     </row>
     <row r="73">
@@ -58979,10 +58979,10 @@
         <v>1</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.3</v>
+        <v>0.8053588248051395</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.5611094693067723</v>
+        <v>1.973136765161561</v>
       </c>
     </row>
     <row r="74">
@@ -59774,10 +59774,10 @@
         <v>1</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.3</v>
+        <v>0.8053588248051395</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.561109697627807</v>
+        <v>1.973136993482596</v>
       </c>
     </row>
     <row r="75">
@@ -60569,10 +60569,10 @@
         <v>1</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.3</v>
+        <v>0.8053588248051395</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.5611089019635953</v>
+        <v>1.973136197818385</v>
       </c>
     </row>
     <row r="76">
@@ -61364,10 +61364,10 @@
         <v>1</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.3</v>
+        <v>0.8053588248051395</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.5611089642329684</v>
+        <v>1.973136260087757</v>
       </c>
     </row>
     <row r="77">
@@ -62159,10 +62159,10 @@
         <v>1</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.3</v>
+        <v>0.8053588248051395</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.5611089919082453</v>
+        <v>1.973136287763035</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>1</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.3</v>
+        <v>0.8053588248051395</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.5611091441222685</v>
+        <v>1.973136439977057</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>1</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.3</v>
+        <v>0.8053588248051395</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.5611087981813068</v>
+        <v>1.973136094036096</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>1</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.3</v>
+        <v>0.8053588248051395</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.5611088742883185</v>
+        <v>1.973136170143107</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>1</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.3</v>
+        <v>0.8053588248051395</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.56110904033998</v>
+        <v>1.973136336194769</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>1</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.3</v>
+        <v>0.8053588248051395</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.5611094001185801</v>
+        <v>1.973136695973369</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>1</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.3</v>
+        <v>0.8053588248051395</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.5611094208750378</v>
+        <v>1.973136716729827</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>1</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.3</v>
+        <v>0.8053588248051395</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.5611095246573263</v>
+        <v>1.973136820512115</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>1</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.3</v>
+        <v>0.8053588248051395</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.561109752978361</v>
+        <v>1.97313704883315</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>1</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.3</v>
+        <v>0.8053588248051395</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.5611096284396148</v>
+        <v>1.973136924294404</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>1</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.3</v>
+        <v>0.8053588248051395</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.5611096561148916</v>
+        <v>1.973136951969681</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>1</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.3</v>
+        <v>0.8053588248051395</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.5611097114654455</v>
+        <v>1.973137007320235</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>1</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.3</v>
+        <v>0.8053588248051395</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.5611099743805763</v>
+        <v>1.973137270235365</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>1</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.3</v>
+        <v>0.8053588248051395</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.5611098913547455</v>
+        <v>1.973137187209534</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>1</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.3</v>
+        <v>0.8053588248051395</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.5611096837901687</v>
+        <v>1.973136979644957</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>1</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.3</v>
+        <v>0.8053588248051395</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.561109697627807</v>
+        <v>1.973136993482596</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>1</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.3</v>
+        <v>0.8053588248051395</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.5611098360041917</v>
+        <v>1.973137131858981</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>1</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.3</v>
+        <v>0.8053588248051395</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.5611095523326032</v>
+        <v>1.973136848187392</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>1</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.3</v>
+        <v>0.8053588248051395</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.5611093793621224</v>
+        <v>1.973136675216911</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>1</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.3</v>
+        <v>0.8053588248051395</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.5611092755798339</v>
+        <v>1.973136571434623</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>1</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.3</v>
+        <v>0.8053588248051395</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.5611094208750378</v>
+        <v>1.973136716729827</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>1</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.3</v>
+        <v>0.8053588248051395</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.561109663033711</v>
+        <v>1.9731369588885</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>1</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.3</v>
+        <v>0.8053588248051395</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.5611094900632301</v>
+        <v>1.973136785918019</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>1</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.3</v>
+        <v>0.8053588248051395</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.561109192554003</v>
+        <v>1.973136488408792</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>1</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.3</v>
+        <v>0.8053588248051395</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.5611091787163646</v>
+        <v>1.973136474571153</v>
       </c>
     </row>
     <row r="102">
@@ -82031,13 +82031,13 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.3</v>
+        <v>-2.073179781458244</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.5611088120189454</v>
+        <v>1.973136107873734</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>1</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.3</v>
+        <v>0.8053588248051395</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.5611088120189454</v>
+        <v>1.973136107873734</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.3</v>
+        <v>-2.073179781458244</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.5611087497495723</v>
+        <v>1.973136045604361</v>
       </c>
     </row>
     <row r="105">
@@ -84416,13 +84416,13 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.3</v>
+        <v>-2.073179781458244</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.5611086459672837</v>
+        <v>1.973135941822072</v>
       </c>
     </row>
     <row r="106">
@@ -85211,13 +85211,13 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.3</v>
+        <v>-2.073179781458244</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.561108472996803</v>
+        <v>1.973135768851592</v>
       </c>
     </row>
     <row r="107">
@@ -86006,13 +86006,13 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.3</v>
+        <v>-2.073179781458244</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.5611085214285375</v>
+        <v>1.973135817283326</v>
       </c>
     </row>
     <row r="108">
@@ -86801,13 +86801,13 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.3</v>
+        <v>-2.073179781458244</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.5611081616499375</v>
+        <v>1.973135457504726</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.3</v>
+        <v>-2.073179781458244</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.5611081201370222</v>
+        <v>1.973135415991811</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.3</v>
+        <v>-2.073179781458244</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.5611081754875759</v>
+        <v>1.973135471342365</v>
       </c>
     </row>
     <row r="111">
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.3</v>
+        <v>-2.073179781458244</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.5611082308381298</v>
+        <v>1.973135526692919</v>
       </c>
     </row>
     <row r="112">
@@ -89981,13 +89981,13 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.3</v>
+        <v>-2.073179781458244</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.5611082723510452</v>
+        <v>1.973135568205834</v>
       </c>
     </row>
     <row r="113">
@@ -90776,13 +90776,13 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.3</v>
+        <v>-2.073179781458244</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.561108002517095</v>
+        <v>1.973135298371884</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.3</v>
+        <v>-2.073179781458244</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.5611080578676491</v>
+        <v>1.973135353722438</v>
       </c>
     </row>
     <row r="115">
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.3</v>
+        <v>-2.073179781458244</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.5611082031628529</v>
+        <v>1.973135499017642</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.3</v>
+        <v>-2.073179781458244</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.5611081685687567</v>
+        <v>1.973135464423546</v>
       </c>
     </row>
     <row r="117">
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.3</v>
+        <v>-2.073179781458244</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.5611081547311181</v>
+        <v>1.973135450585907</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.3</v>
+        <v>-2.073179781458244</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.5611082446757683</v>
+        <v>1.973135540530557</v>
       </c>
     </row>
     <row r="119">
@@ -95546,13 +95546,13 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.3</v>
+        <v>-2.073179781458244</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.5611085629414529</v>
+        <v>1.973135858796242</v>
       </c>
     </row>
     <row r="120">
@@ -96341,13 +96341,13 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.3</v>
+        <v>-2.073179781458244</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.5611083830521528</v>
+        <v>1.973135678906942</v>
       </c>
     </row>
     <row r="121">
@@ -97136,13 +97136,13 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.3</v>
+        <v>-2.073179781458244</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.5611084245650683</v>
+        <v>1.973135720419857</v>
       </c>
     </row>
     <row r="122">
@@ -97931,13 +97931,13 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.3</v>
+        <v>-2.073179781458244</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.561108237756949</v>
+        <v>1.973135533611738</v>
       </c>
     </row>
     <row r="123">
@@ -98726,13 +98726,13 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.3</v>
+        <v>-2.073179781458244</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.5611083069451414</v>
+        <v>1.97313560279993</v>
       </c>
     </row>
     <row r="124">
@@ -99521,13 +99521,13 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.3</v>
+        <v>-2.073179781458244</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.5611081062993836</v>
+        <v>1.973135402154173</v>
       </c>
     </row>
     <row r="125">
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.3</v>
+        <v>-2.073179781458244</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.561108147812299</v>
+        <v>1.973135443667088</v>
       </c>
     </row>
     <row r="126">
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.3</v>
+        <v>-2.073179781458244</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.5611081754875759</v>
+        <v>1.973135471342365</v>
       </c>
     </row>
   </sheetData>

--- a/out/Attention_Base_repeat_3_000006.xlsx
+++ b/out/Attention_Base_repeat_3_000006.xlsx
@@ -2534,7 +2534,7 @@
         <v>1</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>1</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>1</v>
       </c>
       <c r="JB4" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>1</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>1</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>1</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>1</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>1</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>1</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>1</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>1</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>1</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>1</v>
       </c>
       <c r="JB14" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>1</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>1</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>1</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>1</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>1</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>1</v>
       </c>
       <c r="JB20" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>1</v>
       </c>
       <c r="JB21" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>1</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>1</v>
       </c>
       <c r="JB23" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>1</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>1</v>
       </c>
       <c r="JB25" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>1</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>1</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>1</v>
       </c>
       <c r="JB28" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>1</v>
       </c>
       <c r="JB29" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>1</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>1</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>1</v>
       </c>
       <c r="JB32" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>1</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>1</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>1</v>
       </c>
       <c r="JB35" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>1</v>
       </c>
       <c r="JB36" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>1</v>
       </c>
       <c r="JB37" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>1</v>
       </c>
       <c r="JB38" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,7 +31949,7 @@
         <v>1</v>
       </c>
       <c r="JB39" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32744,7 +32744,7 @@
         <v>1</v>
       </c>
       <c r="JB40" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33539,7 +33539,7 @@
         <v>1</v>
       </c>
       <c r="JB41" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>1</v>
       </c>
       <c r="JB42" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35129,7 +35129,7 @@
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35917,17 +35917,17 @@
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA44" t="n">
         <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC44" t="n">
-        <v>-6.556325642217417e-05</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -36708,21 +36708,21 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.08438480768506497</v>
+        <v>0</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA45" t="n">
         <v>1</v>
       </c>
       <c r="JB45" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC45" t="n">
-        <v>0.1689297339021736</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -37503,21 +37503,21 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.0194880177913958</v>
+        <v>0</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
-          <t>StopLoss</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA46" t="n">
         <v>1</v>
       </c>
       <c r="JB46" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC46" t="n">
-        <v>0.06483122663724702</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -38302,17 +38302,17 @@
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA47" t="n">
         <v>1</v>
       </c>
       <c r="JB47" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC47" t="n">
-        <v>0.06483122663724702</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -39097,17 +39097,17 @@
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA48" t="n">
         <v>1</v>
       </c>
       <c r="JB48" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC48" t="n">
-        <v>0.06475166442322568</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -39888,21 +39888,21 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.2444321660704994</v>
+        <v>0</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA49" t="n">
         <v>1</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC49" t="n">
-        <v>0.5541030433219986</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50">
@@ -40683,21 +40683,21 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.0467694028973443</v>
+        <v>0</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA50" t="n">
         <v>1</v>
       </c>
       <c r="JB50" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC50" t="n">
-        <v>0.4028526571241431</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -41478,21 +41478,21 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.08192082715885056</v>
+        <v>0</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA51" t="n">
         <v>1</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC51" t="n">
-        <v>0.5199482700256048</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -42273,21 +42273,21 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.04486282609988666</v>
+        <v>0</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA52" t="n">
         <v>1</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC52" t="n">
-        <v>0.527682525776231</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -43068,21 +43068,21 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.01852900052948198</v>
+        <v>0</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA53" t="n">
         <v>1</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC53" t="n">
-        <v>0.5198305874830726</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -43863,21 +43863,21 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.02308603502812542</v>
+        <v>0</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA54" t="n">
         <v>1</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC54" t="n">
-        <v>0.5474763734630048</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -44658,21 +44658,21 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.01389973439154032</v>
+        <v>0</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA55" t="n">
         <v>1</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC55" t="n">
-        <v>0.5521757733858368</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56">
@@ -45453,21 +45453,21 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.01056623891274916</v>
+        <v>0</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA56" t="n">
         <v>1</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC56" t="n">
-        <v>0.5594043808195763</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -46248,21 +46248,21 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>0.004670697256883739</v>
+        <v>0</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA57" t="n">
         <v>1</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC57" t="n">
-        <v>0.5581718723189736</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58">
@@ -47043,21 +47043,21 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>0.003705173577296268</v>
+        <v>0</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA58" t="n">
         <v>1</v>
       </c>
       <c r="JB58" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC58" t="n">
-        <v>0.5609111095432001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59">
@@ -47838,21 +47838,21 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>0.001836089473792515</v>
+        <v>0</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA59" t="n">
         <v>1</v>
       </c>
       <c r="JB59" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC59" t="n">
-        <v>0.5608732506654687</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60">
@@ -48633,21 +48633,21 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.001065585874391671</v>
+        <v>0</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA60" t="n">
         <v>1</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.561167360520143</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61">
@@ -49428,21 +49428,21 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.0005302929371958355</v>
+        <v>0</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA61" t="n">
         <v>1</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.5611616940443013</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62">
@@ -50223,21 +50223,21 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.0002594676309391166</v>
+        <v>0</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA62" t="n">
         <v>1</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.5611499993118744</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63">
@@ -51018,21 +51018,21 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.0001485320277835259</v>
+        <v>0</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA63" t="n">
         <v>1</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.5611874566156971</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64">
@@ -51813,21 +51813,21 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>4.633531262135388e-05</v>
+        <v>0</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA64" t="n">
         <v>1</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.5611314695106868</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65">
@@ -52608,21 +52608,21 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>1.970370261998147e-05</v>
+        <v>0</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA65" t="n">
         <v>1</v>
       </c>
       <c r="JB65" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.5611267567002347</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66">
@@ -53403,21 +53403,21 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>9.677176780651038e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA66" t="n">
         <v>1</v>
       </c>
       <c r="JB66" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.5611241460540584</v>
+        <v>0</v>
       </c>
     </row>
     <row r="67">
@@ -54198,21 +54198,21 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>2.110541340889784e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA67" t="n">
         <v>1</v>
       </c>
       <c r="JB67" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.5611186804883393</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68">
@@ -54993,21 +54993,21 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>-2.090799254370459e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA68" t="n">
         <v>1</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.5611152958698885</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69">
@@ -55788,21 +55788,21 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>-2.422504053549707e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA69" t="n">
         <v>1</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.5611096284396148</v>
+        <v>0</v>
       </c>
     </row>
     <row r="70">
@@ -56587,17 +56587,17 @@
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA70" t="n">
         <v>1</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.5611100089746726</v>
+        <v>0</v>
       </c>
     </row>
     <row r="71">
@@ -57382,17 +57382,17 @@
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA71" t="n">
         <v>1</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.5611102372957072</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72">
@@ -58177,17 +58177,17 @@
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA72" t="n">
         <v>1</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.5611103272403571</v>
+        <v>0</v>
       </c>
     </row>
     <row r="73">
@@ -58972,17 +58972,17 @@
       </c>
       <c r="IZ73" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA73" t="n">
         <v>1</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.5611094693067723</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74">
@@ -59767,17 +59767,17 @@
       </c>
       <c r="IZ74" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA74" t="n">
         <v>1</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.561109697627807</v>
+        <v>0</v>
       </c>
     </row>
     <row r="75">
@@ -60562,17 +60562,17 @@
       </c>
       <c r="IZ75" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA75" t="n">
         <v>1</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.5611089019635953</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76">
@@ -61357,17 +61357,17 @@
       </c>
       <c r="IZ76" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA76" t="n">
         <v>1</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.5611089642329684</v>
+        <v>0</v>
       </c>
     </row>
     <row r="77">
@@ -62152,17 +62152,17 @@
       </c>
       <c r="IZ77" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA77" t="n">
         <v>1</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.5611089919082453</v>
+        <v>0</v>
       </c>
     </row>
     <row r="78">
@@ -62947,17 +62947,17 @@
       </c>
       <c r="IZ78" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA78" t="n">
         <v>1</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.5611091441222685</v>
+        <v>0</v>
       </c>
     </row>
     <row r="79">
@@ -63742,17 +63742,17 @@
       </c>
       <c r="IZ79" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA79" t="n">
         <v>1</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.5611087981813068</v>
+        <v>0</v>
       </c>
     </row>
     <row r="80">
@@ -64537,17 +64537,17 @@
       </c>
       <c r="IZ80" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA80" t="n">
         <v>1</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.5611088742883185</v>
+        <v>0</v>
       </c>
     </row>
     <row r="81">
@@ -65332,17 +65332,17 @@
       </c>
       <c r="IZ81" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA81" t="n">
         <v>1</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.56110904033998</v>
+        <v>0</v>
       </c>
     </row>
     <row r="82">
@@ -66127,17 +66127,17 @@
       </c>
       <c r="IZ82" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA82" t="n">
         <v>1</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.5611094001185801</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83">
@@ -66922,17 +66922,17 @@
       </c>
       <c r="IZ83" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA83" t="n">
         <v>1</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.5611094208750378</v>
+        <v>0</v>
       </c>
     </row>
     <row r="84">
@@ -67717,17 +67717,17 @@
       </c>
       <c r="IZ84" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA84" t="n">
         <v>1</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.5611095246573263</v>
+        <v>0</v>
       </c>
     </row>
     <row r="85">
@@ -68512,17 +68512,17 @@
       </c>
       <c r="IZ85" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA85" t="n">
         <v>1</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.561109752978361</v>
+        <v>0</v>
       </c>
     </row>
     <row r="86">
@@ -69307,17 +69307,17 @@
       </c>
       <c r="IZ86" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA86" t="n">
         <v>1</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.5611096284396148</v>
+        <v>0</v>
       </c>
     </row>
     <row r="87">
@@ -70102,17 +70102,17 @@
       </c>
       <c r="IZ87" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA87" t="n">
         <v>1</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.5611096561148916</v>
+        <v>0</v>
       </c>
     </row>
     <row r="88">
@@ -70897,17 +70897,17 @@
       </c>
       <c r="IZ88" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA88" t="n">
         <v>1</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.5611097114654455</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89">
@@ -71692,17 +71692,17 @@
       </c>
       <c r="IZ89" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA89" t="n">
         <v>1</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.5611099743805763</v>
+        <v>0</v>
       </c>
     </row>
     <row r="90">
@@ -72487,17 +72487,17 @@
       </c>
       <c r="IZ90" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA90" t="n">
         <v>1</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.5611098913547455</v>
+        <v>0</v>
       </c>
     </row>
     <row r="91">
@@ -73282,17 +73282,17 @@
       </c>
       <c r="IZ91" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA91" t="n">
         <v>1</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.5611096837901687</v>
+        <v>0</v>
       </c>
     </row>
     <row r="92">
@@ -74077,17 +74077,17 @@
       </c>
       <c r="IZ92" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA92" t="n">
         <v>1</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.561109697627807</v>
+        <v>0</v>
       </c>
     </row>
     <row r="93">
@@ -74872,17 +74872,17 @@
       </c>
       <c r="IZ93" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA93" t="n">
         <v>1</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.5611098360041917</v>
+        <v>0</v>
       </c>
     </row>
     <row r="94">
@@ -75667,17 +75667,17 @@
       </c>
       <c r="IZ94" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA94" t="n">
         <v>1</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.5611095523326032</v>
+        <v>0</v>
       </c>
     </row>
     <row r="95">
@@ -76462,17 +76462,17 @@
       </c>
       <c r="IZ95" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA95" t="n">
         <v>1</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.5611093793621224</v>
+        <v>0</v>
       </c>
     </row>
     <row r="96">
@@ -77257,17 +77257,17 @@
       </c>
       <c r="IZ96" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA96" t="n">
         <v>1</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.5611092755798339</v>
+        <v>0</v>
       </c>
     </row>
     <row r="97">
@@ -78052,17 +78052,17 @@
       </c>
       <c r="IZ97" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA97" t="n">
         <v>1</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.5611094208750378</v>
+        <v>0</v>
       </c>
     </row>
     <row r="98">
@@ -78847,17 +78847,17 @@
       </c>
       <c r="IZ98" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA98" t="n">
         <v>1</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.561109663033711</v>
+        <v>0</v>
       </c>
     </row>
     <row r="99">
@@ -79642,17 +79642,17 @@
       </c>
       <c r="IZ99" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA99" t="n">
         <v>1</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.5611094900632301</v>
+        <v>0</v>
       </c>
     </row>
     <row r="100">
@@ -80437,17 +80437,17 @@
       </c>
       <c r="IZ100" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA100" t="n">
         <v>1</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.561109192554003</v>
+        <v>0</v>
       </c>
     </row>
     <row r="101">
@@ -81232,17 +81232,17 @@
       </c>
       <c r="IZ101" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA101" t="n">
         <v>1</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.5611091787163646</v>
+        <v>0</v>
       </c>
     </row>
     <row r="102">
@@ -82027,17 +82027,17 @@
       </c>
       <c r="IZ102" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA102" t="n">
         <v>1</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.5611088120189454</v>
+        <v>0</v>
       </c>
     </row>
     <row r="103">
@@ -82822,17 +82822,17 @@
       </c>
       <c r="IZ103" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA103" t="n">
         <v>1</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.5611088120189454</v>
+        <v>0</v>
       </c>
     </row>
     <row r="104">
@@ -83617,17 +83617,17 @@
       </c>
       <c r="IZ104" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA104" t="n">
         <v>1</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.5611087497495723</v>
+        <v>0</v>
       </c>
     </row>
     <row r="105">
@@ -84412,17 +84412,17 @@
       </c>
       <c r="IZ105" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA105" t="n">
         <v>1</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.5611086459672837</v>
+        <v>0</v>
       </c>
     </row>
     <row r="106">
@@ -85207,17 +85207,17 @@
       </c>
       <c r="IZ106" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA106" t="n">
         <v>1</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.561108472996803</v>
+        <v>0</v>
       </c>
     </row>
     <row r="107">
@@ -86002,17 +86002,17 @@
       </c>
       <c r="IZ107" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA107" t="n">
         <v>1</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.5611085214285375</v>
+        <v>0</v>
       </c>
     </row>
     <row r="108">
@@ -86797,17 +86797,17 @@
       </c>
       <c r="IZ108" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA108" t="n">
         <v>1</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.5611081616499375</v>
+        <v>0</v>
       </c>
     </row>
     <row r="109">
@@ -87592,17 +87592,17 @@
       </c>
       <c r="IZ109" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA109" t="n">
         <v>1</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.5611081201370222</v>
+        <v>0</v>
       </c>
     </row>
     <row r="110">
@@ -88387,17 +88387,17 @@
       </c>
       <c r="IZ110" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA110" t="n">
         <v>1</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.5611081754875759</v>
+        <v>0</v>
       </c>
     </row>
     <row r="111">
@@ -89182,17 +89182,17 @@
       </c>
       <c r="IZ111" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA111" t="n">
         <v>1</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.5611082308381298</v>
+        <v>0</v>
       </c>
     </row>
     <row r="112">
@@ -89977,17 +89977,17 @@
       </c>
       <c r="IZ112" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA112" t="n">
         <v>1</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.5611082723510452</v>
+        <v>0</v>
       </c>
     </row>
     <row r="113">
@@ -90772,17 +90772,17 @@
       </c>
       <c r="IZ113" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA113" t="n">
         <v>1</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.561108002517095</v>
+        <v>0</v>
       </c>
     </row>
     <row r="114">
@@ -91567,17 +91567,17 @@
       </c>
       <c r="IZ114" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA114" t="n">
         <v>1</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.5611080578676491</v>
+        <v>0</v>
       </c>
     </row>
     <row r="115">
@@ -92362,17 +92362,17 @@
       </c>
       <c r="IZ115" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA115" t="n">
         <v>1</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.5611082031628529</v>
+        <v>0</v>
       </c>
     </row>
     <row r="116">
@@ -93157,17 +93157,17 @@
       </c>
       <c r="IZ116" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA116" t="n">
         <v>1</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.5611081685687567</v>
+        <v>0</v>
       </c>
     </row>
     <row r="117">
@@ -93952,17 +93952,17 @@
       </c>
       <c r="IZ117" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA117" t="n">
         <v>1</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.5611081547311181</v>
+        <v>0</v>
       </c>
     </row>
     <row r="118">
@@ -94747,17 +94747,17 @@
       </c>
       <c r="IZ118" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA118" t="n">
         <v>1</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.5611082446757683</v>
+        <v>0</v>
       </c>
     </row>
     <row r="119">
@@ -95542,17 +95542,17 @@
       </c>
       <c r="IZ119" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA119" t="n">
         <v>1</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.5611085629414529</v>
+        <v>0</v>
       </c>
     </row>
     <row r="120">
@@ -96337,17 +96337,17 @@
       </c>
       <c r="IZ120" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA120" t="n">
         <v>1</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.5611083830521528</v>
+        <v>0</v>
       </c>
     </row>
     <row r="121">
@@ -97132,17 +97132,17 @@
       </c>
       <c r="IZ121" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA121" t="n">
         <v>1</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.5611084245650683</v>
+        <v>0</v>
       </c>
     </row>
     <row r="122">
@@ -97927,17 +97927,17 @@
       </c>
       <c r="IZ122" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA122" t="n">
         <v>1</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.561108237756949</v>
+        <v>0</v>
       </c>
     </row>
     <row r="123">
@@ -98722,17 +98722,17 @@
       </c>
       <c r="IZ123" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA123" t="n">
         <v>1</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.5611083069451414</v>
+        <v>0</v>
       </c>
     </row>
     <row r="124">
@@ -99517,17 +99517,17 @@
       </c>
       <c r="IZ124" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA124" t="n">
         <v>1</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.5611081062993836</v>
+        <v>0</v>
       </c>
     </row>
     <row r="125">
@@ -100312,17 +100312,17 @@
       </c>
       <c r="IZ125" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA125" t="n">
         <v>1</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.561108147812299</v>
+        <v>0</v>
       </c>
     </row>
     <row r="126">
@@ -101103,21 +101103,21 @@
         <v>0</v>
       </c>
       <c r="IY126" t="n">
-        <v>-3.873712549958921e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ126" t="inlineStr">
         <is>
-          <t>Sell (Force)</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA126" t="n">
         <v>1</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.5611081754875759</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/out/Attention_Base_repeat_3_000006.xlsx
+++ b/out/Attention_Base_repeat_3_000006.xlsx
@@ -1731,12 +1731,12 @@
       </c>
       <c r="JA1" s="1" t="inlineStr">
         <is>
-          <t>Predicted Value</t>
+          <t>Original Prediction</t>
         </is>
       </c>
       <c r="JB1" s="1" t="inlineStr">
         <is>
-          <t>Enhanced Signal</t>
+          <t>Trading Signal</t>
         </is>
       </c>
       <c r="JC1" s="1" t="inlineStr">
@@ -2531,10 +2531,10 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>1</v>
+        <v>0.008324789814651012</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3326,10 +3326,10 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>1</v>
+        <v>0.008959507569670677</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4121,10 +4121,10 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>1</v>
+        <v>0.009910263121128082</v>
       </c>
       <c r="JB4" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4916,10 +4916,10 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>1</v>
+        <v>0.01182365976274014</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>1</v>
+        <v>0.01147877238690853</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6506,10 +6506,10 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>1</v>
+        <v>0.0118190199136734</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7301,10 +7301,10 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>1</v>
+        <v>0.01069262344390154</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8096,10 +8096,10 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>1</v>
+        <v>0.01138768438249826</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8891,10 +8891,10 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>1</v>
+        <v>0.01210763119161129</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9686,10 +9686,10 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>1</v>
+        <v>0.0119902677834034</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10481,10 +10481,10 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>1</v>
+        <v>0.01126126851886511</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11276,10 +11276,10 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>1</v>
+        <v>0.01025288552045822</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12071,10 +12071,10 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>1</v>
+        <v>0.01022199261933565</v>
       </c>
       <c r="JB14" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12866,10 +12866,10 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>1</v>
+        <v>0.009632938541471958</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13661,10 +13661,10 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>1</v>
+        <v>0.009029914624989033</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14456,10 +14456,10 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>1</v>
+        <v>0.008419930934906006</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15251,10 +15251,10 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>1</v>
+        <v>0.008208390325307846</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16046,10 +16046,10 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>1</v>
+        <v>0.008329130709171295</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16837,14 +16837,14 @@
       </c>
       <c r="IZ20" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>1</v>
+        <v>0.008944384753704071</v>
       </c>
       <c r="JB20" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17632,14 +17632,14 @@
       </c>
       <c r="IZ21" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>1</v>
+        <v>0.008967593312263489</v>
       </c>
       <c r="JB21" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18427,14 +18427,14 @@
       </c>
       <c r="IZ22" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>1</v>
+        <v>0.008884737268090248</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19222,14 +19222,14 @@
       </c>
       <c r="IZ23" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>1</v>
+        <v>0.008519439958035946</v>
       </c>
       <c r="JB23" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20017,14 +20017,14 @@
       </c>
       <c r="IZ24" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>1</v>
+        <v>0.008296424522995949</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20812,14 +20812,14 @@
       </c>
       <c r="IZ25" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>1</v>
+        <v>0.008580663241446018</v>
       </c>
       <c r="JB25" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21607,14 +21607,14 @@
       </c>
       <c r="IZ26" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>1</v>
+        <v>0.008422245271503925</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.16</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22402,14 +22402,14 @@
       </c>
       <c r="IZ27" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>1</v>
+        <v>0.008841784670948982</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23197,14 +23197,14 @@
       </c>
       <c r="IZ28" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>1</v>
+        <v>0.01078502647578716</v>
       </c>
       <c r="JB28" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23992,14 +23992,14 @@
       </c>
       <c r="IZ29" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>1</v>
+        <v>0.01132073812186718</v>
       </c>
       <c r="JB29" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24787,14 +24787,14 @@
       </c>
       <c r="IZ30" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>1</v>
+        <v>0.01150371599942446</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25582,14 +25582,14 @@
       </c>
       <c r="IZ31" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>1</v>
+        <v>0.01166610233485699</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26377,14 +26377,14 @@
       </c>
       <c r="IZ32" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>1</v>
+        <v>0.01145157404243946</v>
       </c>
       <c r="JB32" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27172,14 +27172,14 @@
       </c>
       <c r="IZ33" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>1</v>
+        <v>0.01109606493264437</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27967,14 +27967,14 @@
       </c>
       <c r="IZ34" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>1</v>
+        <v>0.01095558889210224</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28762,14 +28762,14 @@
       </c>
       <c r="IZ35" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>1</v>
+        <v>0.01178636960685253</v>
       </c>
       <c r="JB35" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29557,14 +29557,14 @@
       </c>
       <c r="IZ36" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>1</v>
+        <v>0.01192432269454002</v>
       </c>
       <c r="JB36" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30352,14 +30352,14 @@
       </c>
       <c r="IZ37" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>1</v>
+        <v>0.01205925177782774</v>
       </c>
       <c r="JB37" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31147,14 +31147,14 @@
       </c>
       <c r="IZ38" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>1</v>
+        <v>0.01241092383861542</v>
       </c>
       <c r="JB38" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31942,14 +31942,14 @@
       </c>
       <c r="IZ39" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>1</v>
+        <v>0.01238219905644655</v>
       </c>
       <c r="JB39" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32737,14 +32737,14 @@
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>1</v>
+        <v>0.01247273199260235</v>
       </c>
       <c r="JB40" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33532,14 +33532,14 @@
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>1</v>
+        <v>0.01284434646368027</v>
       </c>
       <c r="JB41" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34327,14 +34327,14 @@
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>1</v>
+        <v>0.01364809088408947</v>
       </c>
       <c r="JB42" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35122,14 +35122,14 @@
       </c>
       <c r="IZ43" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>1</v>
+        <v>0.01476133987307549</v>
       </c>
       <c r="JB43" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35917,17 +35917,17 @@
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Buy</t>
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0.01778373494744301</v>
       </c>
       <c r="JB44" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC44" t="n">
-        <v>0</v>
+        <v>-0.0002147892381881829</v>
       </c>
     </row>
     <row r="45">
@@ -36708,21 +36708,21 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0</v>
+        <v>0.2764504808246421</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>1</v>
+        <v>0.02016453817486763</v>
       </c>
       <c r="JB45" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC45" t="n">
-        <v>0</v>
+        <v>0.5534241389394077</v>
       </c>
     </row>
     <row r="46">
@@ -37503,21 +37503,21 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0</v>
+        <v>-0.06384377903018326</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>StopLoss</t>
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>1</v>
+        <v>0.01969841681420803</v>
       </c>
       <c r="JB46" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC46" t="n">
-        <v>0</v>
+        <v>0.2123919125562706</v>
       </c>
     </row>
     <row r="47">
@@ -38302,17 +38302,17 @@
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>1</v>
+        <v>0.02057724073529243</v>
       </c>
       <c r="JB47" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC47" t="n">
-        <v>0</v>
+        <v>0.2123919125562706</v>
       </c>
     </row>
     <row r="48">
@@ -39097,17 +39097,17 @@
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Buy</t>
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>1</v>
+        <v>0.02162159979343414</v>
       </c>
       <c r="JB48" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC48" t="n">
-        <v>0</v>
+        <v>0.2122298046356533</v>
       </c>
     </row>
     <row r="49">
@@ -39888,21 +39888,21 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0</v>
+        <v>0.4980305911061118</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>1</v>
+        <v>0.02186788991093636</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC49" t="n">
-        <v>0</v>
+        <v>1.209282682158428</v>
       </c>
     </row>
     <row r="50">
@@ -40683,21 +40683,21 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0</v>
+        <v>0.09529254197194843</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>1</v>
+        <v>0.02363432012498379</v>
       </c>
       <c r="JB50" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC50" t="n">
-        <v>0</v>
+        <v>0.9011103968147766</v>
       </c>
     </row>
     <row r="51">
@@ -41478,21 +41478,21 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0</v>
+        <v>0.1669137070898244</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>1</v>
+        <v>0.02488146349787712</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC51" t="n">
-        <v>0</v>
+        <v>1.139692416173204</v>
       </c>
     </row>
     <row r="52">
@@ -42273,21 +42273,21 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0</v>
+        <v>0.09140825835360565</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>1</v>
+        <v>0.02630324475467205</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC52" t="n">
-        <v>0</v>
+        <v>1.155450920811961</v>
       </c>
     </row>
     <row r="53">
@@ -43068,21 +43068,21 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0</v>
+        <v>0.03775274509343247</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>1</v>
+        <v>0.0261911153793335</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC53" t="n">
-        <v>0</v>
+        <v>1.139452722294349</v>
       </c>
     </row>
     <row r="54">
@@ -43863,21 +43863,21 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0</v>
+        <v>0.0470371710841986</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>1</v>
+        <v>0.03151402249932289</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC54" t="n">
-        <v>0</v>
+        <v>1.19578026244193</v>
       </c>
     </row>
     <row r="55">
@@ -44658,21 +44658,21 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0</v>
+        <v>0.02832245289538221</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>1</v>
+        <v>0.0310664214193821</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC55" t="n">
-        <v>0</v>
+        <v>1.205356077762987</v>
       </c>
     </row>
     <row r="56">
@@ -45453,21 +45453,21 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0</v>
+        <v>0.02153267807600453</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>1</v>
+        <v>0.04329529404640198</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC56" t="n">
-        <v>0</v>
+        <v>1.220086878489014</v>
       </c>
     </row>
     <row r="57">
@@ -46248,21 +46248,21 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>0</v>
+        <v>0.00952121664097931</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>1</v>
+        <v>0.03565741330385208</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC57" t="n">
-        <v>0</v>
+        <v>1.217581180846076</v>
       </c>
     </row>
     <row r="58">
@@ -47043,21 +47043,21 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>0</v>
+        <v>0.00755406880432149</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>1</v>
+        <v>0.03572268784046173</v>
       </c>
       <c r="JB58" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC58" t="n">
-        <v>0</v>
+        <v>1.223166292073171</v>
       </c>
     </row>
     <row r="59">
@@ -47838,21 +47838,21 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>0</v>
+        <v>0.003744718914694265</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>1</v>
+        <v>0.08531618118286133</v>
       </c>
       <c r="JB59" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC59" t="n">
-        <v>0</v>
+        <v>1.223094368896922</v>
       </c>
     </row>
     <row r="60">
@@ -48633,21 +48633,21 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0</v>
+        <v>0.002173991358476526</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>1</v>
+        <v>0.1141929104924202</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC60" t="n">
-        <v>0</v>
+        <v>1.223698563197341</v>
       </c>
     </row>
     <row r="61">
@@ -49428,21 +49428,21 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0</v>
+        <v>0.001085950279611078</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>1</v>
+        <v>0.0941154882311821</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC61" t="n">
-        <v>0</v>
+        <v>1.223692204890598</v>
       </c>
     </row>
     <row r="62">
@@ -50223,21 +50223,21 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0</v>
+        <v>0.0005325592063653784</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>1</v>
+        <v>0.09206041693687439</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC62" t="n">
-        <v>0</v>
+        <v>1.223673562525156</v>
       </c>
     </row>
     <row r="63">
@@ -51018,21 +51018,21 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0</v>
+        <v>0.0003087393611228572</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>1</v>
+        <v>0.1034247875213623</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC63" t="n">
-        <v>0</v>
+        <v>1.223755323102533</v>
       </c>
     </row>
     <row r="64">
@@ -51813,21 +51813,21 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0</v>
+        <v>9.990259535667968e-05</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>1</v>
+        <v>0.07868546992540359</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC64" t="n">
-        <v>0</v>
+        <v>1.22364613206186</v>
       </c>
     </row>
     <row r="65">
@@ -52608,21 +52608,21 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>0</v>
+        <v>4.665319638723399e-05</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>1</v>
+        <v>0.07886593788862228</v>
       </c>
       <c r="JB65" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.16</v>
       </c>
       <c r="JC65" t="n">
-        <v>0</v>
+        <v>1.22364171745349</v>
       </c>
     </row>
     <row r="66">
@@ -53403,21 +53403,21 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>0</v>
+        <v>2.435435356130208e-05</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>1</v>
+        <v>0.07550032436847687</v>
       </c>
       <c r="JB66" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.3</v>
       </c>
       <c r="JC66" t="n">
-        <v>0</v>
+        <v>1.223641496161138</v>
       </c>
     </row>
     <row r="67">
@@ -54198,21 +54198,21 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>0</v>
+        <v>9.221082681779568e-06</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>1</v>
+        <v>0.08045010268688202</v>
       </c>
       <c r="JB67" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.16</v>
       </c>
       <c r="JC67" t="n">
-        <v>0</v>
+        <v>1.2236355650297</v>
       </c>
     </row>
     <row r="68">
@@ -54993,21 +54993,21 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>0</v>
+        <v>3.727602236888622e-06</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>1</v>
+        <v>0.0898178294301033</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC68" t="n">
-        <v>0</v>
+        <v>1.223633792170647</v>
       </c>
     </row>
     <row r="69">
@@ -55788,21 +55788,21 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>0</v>
+        <v>-2.422504053549707e-06</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>1</v>
+        <v>0.08460680395364761</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC69" t="n">
-        <v>0</v>
+        <v>1.22362779263705</v>
       </c>
     </row>
     <row r="70">
@@ -56583,21 +56583,21 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>0</v>
+        <v>-2.042425637823487e-06</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>1</v>
+        <v>0.09516702592372894</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC70" t="n">
-        <v>0</v>
+        <v>1.223623550026896</v>
       </c>
     </row>
     <row r="71">
@@ -57382,17 +57382,17 @@
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>1</v>
+        <v>0.08683975040912628</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC71" t="n">
-        <v>0</v>
+        <v>1.223623778347931</v>
       </c>
     </row>
     <row r="72">
@@ -58177,17 +58177,17 @@
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>1</v>
+        <v>0.08462465554475784</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC72" t="n">
-        <v>0</v>
+        <v>1.223623868292581</v>
       </c>
     </row>
     <row r="73">
@@ -58972,17 +58972,17 @@
       </c>
       <c r="IZ73" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>1</v>
+        <v>0.07574169337749481</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC73" t="n">
-        <v>0</v>
+        <v>1.223623010358996</v>
       </c>
     </row>
     <row r="74">
@@ -59767,17 +59767,17 @@
       </c>
       <c r="IZ74" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>1</v>
+        <v>0.07824627310037613</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.16</v>
       </c>
       <c r="JC74" t="n">
-        <v>0</v>
+        <v>1.223623238680031</v>
       </c>
     </row>
     <row r="75">
@@ -60562,17 +60562,17 @@
       </c>
       <c r="IZ75" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>1</v>
+        <v>0.07290071249008179</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.3</v>
       </c>
       <c r="JC75" t="n">
-        <v>0</v>
+        <v>1.223622443015819</v>
       </c>
     </row>
     <row r="76">
@@ -61357,17 +61357,17 @@
       </c>
       <c r="IZ76" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>1</v>
+        <v>0.0681551918387413</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.3</v>
       </c>
       <c r="JC76" t="n">
-        <v>0</v>
+        <v>1.223622505285192</v>
       </c>
     </row>
     <row r="77">
@@ -62152,17 +62152,17 @@
       </c>
       <c r="IZ77" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>1</v>
+        <v>0.06900878995656967</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.3</v>
       </c>
       <c r="JC77" t="n">
-        <v>0</v>
+        <v>1.223622532960469</v>
       </c>
     </row>
     <row r="78">
@@ -62947,17 +62947,17 @@
       </c>
       <c r="IZ78" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>1</v>
+        <v>0.07259701192378998</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC78" t="n">
-        <v>0</v>
+        <v>1.223622685174492</v>
       </c>
     </row>
     <row r="79">
@@ -63742,17 +63742,17 @@
       </c>
       <c r="IZ79" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>1</v>
+        <v>0.06647990643978119</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC79" t="n">
-        <v>0</v>
+        <v>1.223622339233531</v>
       </c>
     </row>
     <row r="80">
@@ -64537,17 +64537,17 @@
       </c>
       <c r="IZ80" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>1</v>
+        <v>0.06724502146244049</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC80" t="n">
-        <v>0</v>
+        <v>1.223622415340542</v>
       </c>
     </row>
     <row r="81">
@@ -65332,17 +65332,17 @@
       </c>
       <c r="IZ81" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>1</v>
+        <v>0.06442661583423615</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC81" t="n">
-        <v>0</v>
+        <v>1.223622581392204</v>
       </c>
     </row>
     <row r="82">
@@ -66127,17 +66127,17 @@
       </c>
       <c r="IZ82" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>1</v>
+        <v>0.07266802340745926</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.3</v>
       </c>
       <c r="JC82" t="n">
-        <v>0</v>
+        <v>1.223622941170804</v>
       </c>
     </row>
     <row r="83">
@@ -66922,17 +66922,17 @@
       </c>
       <c r="IZ83" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>1</v>
+        <v>0.07711952179670334</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC83" t="n">
-        <v>0</v>
+        <v>1.223622961927262</v>
       </c>
     </row>
     <row r="84">
@@ -67717,17 +67717,17 @@
       </c>
       <c r="IZ84" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>1</v>
+        <v>0.08156725019216537</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC84" t="n">
-        <v>0</v>
+        <v>1.22362306570955</v>
       </c>
     </row>
     <row r="85">
@@ -68512,17 +68512,17 @@
       </c>
       <c r="IZ85" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>1</v>
+        <v>0.07631438970565796</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.3</v>
       </c>
       <c r="JC85" t="n">
-        <v>0</v>
+        <v>1.223623294030585</v>
       </c>
     </row>
     <row r="86">
@@ -69307,17 +69307,17 @@
       </c>
       <c r="IZ86" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>1</v>
+        <v>0.07248599082231522</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC86" t="n">
-        <v>0</v>
+        <v>1.223623169491839</v>
       </c>
     </row>
     <row r="87">
@@ -70102,17 +70102,17 @@
       </c>
       <c r="IZ87" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>1</v>
+        <v>0.06914449483156204</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC87" t="n">
-        <v>0</v>
+        <v>1.223623197167116</v>
       </c>
     </row>
     <row r="88">
@@ -70897,17 +70897,17 @@
       </c>
       <c r="IZ88" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>1</v>
+        <v>0.07720334827899933</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC88" t="n">
-        <v>0</v>
+        <v>1.22362325251767</v>
       </c>
     </row>
     <row r="89">
@@ -71692,17 +71692,17 @@
       </c>
       <c r="IZ89" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>1</v>
+        <v>0.07359380275011063</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC89" t="n">
-        <v>0</v>
+        <v>1.2236235154328</v>
       </c>
     </row>
     <row r="90">
@@ -72487,17 +72487,17 @@
       </c>
       <c r="IZ90" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>1</v>
+        <v>0.0723477378487587</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC90" t="n">
-        <v>0</v>
+        <v>1.223623432406969</v>
       </c>
     </row>
     <row r="91">
@@ -73282,17 +73282,17 @@
       </c>
       <c r="IZ91" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>1</v>
+        <v>0.06966348737478256</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC91" t="n">
-        <v>0</v>
+        <v>1.223623224842392</v>
       </c>
     </row>
     <row r="92">
@@ -74077,17 +74077,17 @@
       </c>
       <c r="IZ92" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>1</v>
+        <v>0.06906706094741821</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC92" t="n">
-        <v>0</v>
+        <v>1.223623238680031</v>
       </c>
     </row>
     <row r="93">
@@ -74872,17 +74872,17 @@
       </c>
       <c r="IZ93" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>1</v>
+        <v>0.06864035129547119</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC93" t="n">
-        <v>0</v>
+        <v>1.223623377056416</v>
       </c>
     </row>
     <row r="94">
@@ -75667,17 +75667,17 @@
       </c>
       <c r="IZ94" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>1</v>
+        <v>0.06521400809288025</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC94" t="n">
-        <v>0</v>
+        <v>1.223623093384827</v>
       </c>
     </row>
     <row r="95">
@@ -76462,17 +76462,17 @@
       </c>
       <c r="IZ95" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>1</v>
+        <v>0.06216628849506378</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC95" t="n">
-        <v>0</v>
+        <v>1.223622920414346</v>
       </c>
     </row>
     <row r="96">
@@ -77257,17 +77257,17 @@
       </c>
       <c r="IZ96" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>1</v>
+        <v>0.06488651037216187</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC96" t="n">
-        <v>0</v>
+        <v>1.223622816632058</v>
       </c>
     </row>
     <row r="97">
@@ -78052,17 +78052,17 @@
       </c>
       <c r="IZ97" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>1</v>
+        <v>0.06412804126739502</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC97" t="n">
-        <v>0</v>
+        <v>1.223622961927262</v>
       </c>
     </row>
     <row r="98">
@@ -78847,17 +78847,17 @@
       </c>
       <c r="IZ98" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>1</v>
+        <v>0.06372403353452682</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC98" t="n">
-        <v>0</v>
+        <v>1.223623204085935</v>
       </c>
     </row>
     <row r="99">
@@ -79642,17 +79642,17 @@
       </c>
       <c r="IZ99" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>1</v>
+        <v>0.06163204461336136</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC99" t="n">
-        <v>0</v>
+        <v>1.223623031115454</v>
       </c>
     </row>
     <row r="100">
@@ -80437,17 +80437,17 @@
       </c>
       <c r="IZ100" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>1</v>
+        <v>0.05785417556762695</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC100" t="n">
-        <v>0</v>
+        <v>1.223622733606227</v>
       </c>
     </row>
     <row r="101">
@@ -81232,17 +81232,17 @@
       </c>
       <c r="IZ101" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>1</v>
+        <v>0.05710297077894211</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC101" t="n">
-        <v>0</v>
+        <v>1.223622719768588</v>
       </c>
     </row>
     <row r="102">
@@ -82027,17 +82027,17 @@
       </c>
       <c r="IZ102" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>1</v>
+        <v>0.05399446189403534</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC102" t="n">
-        <v>0</v>
+        <v>1.223622353071169</v>
       </c>
     </row>
     <row r="103">
@@ -82822,17 +82822,17 @@
       </c>
       <c r="IZ103" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>1</v>
+        <v>0.05517891049385071</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC103" t="n">
-        <v>0</v>
+        <v>1.223622353071169</v>
       </c>
     </row>
     <row r="104">
@@ -83617,17 +83617,17 @@
       </c>
       <c r="IZ104" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>1</v>
+        <v>0.05637591332197189</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC104" t="n">
-        <v>0</v>
+        <v>1.223622290801796</v>
       </c>
     </row>
     <row r="105">
@@ -84412,17 +84412,17 @@
       </c>
       <c r="IZ105" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>1</v>
+        <v>0.0518110916018486</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC105" t="n">
-        <v>0</v>
+        <v>1.223622187019507</v>
       </c>
     </row>
     <row r="106">
@@ -85207,17 +85207,17 @@
       </c>
       <c r="IZ106" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>1</v>
+        <v>0.05080610513687134</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC106" t="n">
-        <v>0</v>
+        <v>1.223622014049027</v>
       </c>
     </row>
     <row r="107">
@@ -86002,17 +86002,17 @@
       </c>
       <c r="IZ107" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>1</v>
+        <v>0.05018085986375809</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC107" t="n">
-        <v>0</v>
+        <v>1.223622062480761</v>
       </c>
     </row>
     <row r="108">
@@ -86797,17 +86797,17 @@
       </c>
       <c r="IZ108" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>1</v>
+        <v>0.04739109426736832</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC108" t="n">
-        <v>0</v>
+        <v>1.223621702702161</v>
       </c>
     </row>
     <row r="109">
@@ -87592,17 +87592,17 @@
       </c>
       <c r="IZ109" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>1</v>
+        <v>0.04647547006607056</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC109" t="n">
-        <v>0</v>
+        <v>1.223621661189246</v>
       </c>
     </row>
     <row r="110">
@@ -88387,17 +88387,17 @@
       </c>
       <c r="IZ110" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>1</v>
+        <v>0.04763497039675713</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC110" t="n">
-        <v>0</v>
+        <v>1.2236217165398</v>
       </c>
     </row>
     <row r="111">
@@ -89182,17 +89182,17 @@
       </c>
       <c r="IZ111" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>1</v>
+        <v>0.04602303355932236</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC111" t="n">
-        <v>0</v>
+        <v>1.223621771890354</v>
       </c>
     </row>
     <row r="112">
@@ -89977,17 +89977,17 @@
       </c>
       <c r="IZ112" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>1</v>
+        <v>0.04559382796287537</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC112" t="n">
-        <v>0</v>
+        <v>1.223621813403269</v>
       </c>
     </row>
     <row r="113">
@@ -90772,17 +90772,17 @@
       </c>
       <c r="IZ113" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>1</v>
+        <v>0.04378011077642441</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC113" t="n">
-        <v>0</v>
+        <v>1.223621543569319</v>
       </c>
     </row>
     <row r="114">
@@ -91567,17 +91567,17 @@
       </c>
       <c r="IZ114" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>1</v>
+        <v>0.0440521165728569</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC114" t="n">
-        <v>0</v>
+        <v>1.223621598919873</v>
       </c>
     </row>
     <row r="115">
@@ -92362,17 +92362,17 @@
       </c>
       <c r="IZ115" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>1</v>
+        <v>0.04397844895720482</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC115" t="n">
-        <v>0</v>
+        <v>1.223621744215077</v>
       </c>
     </row>
     <row r="116">
@@ -93157,17 +93157,17 @@
       </c>
       <c r="IZ116" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>1</v>
+        <v>0.0436248779296875</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC116" t="n">
-        <v>0</v>
+        <v>1.22362170962098</v>
       </c>
     </row>
     <row r="117">
@@ -93952,17 +93952,17 @@
       </c>
       <c r="IZ117" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>1</v>
+        <v>0.04272929206490517</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC117" t="n">
-        <v>0</v>
+        <v>1.223621695783342</v>
       </c>
     </row>
     <row r="118">
@@ -94747,17 +94747,17 @@
       </c>
       <c r="IZ118" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>1</v>
+        <v>0.04566066712141037</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC118" t="n">
-        <v>0</v>
+        <v>1.223621785727992</v>
       </c>
     </row>
     <row r="119">
@@ -95542,17 +95542,17 @@
       </c>
       <c r="IZ119" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>1</v>
+        <v>0.05374690145254135</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC119" t="n">
-        <v>0</v>
+        <v>1.223622103993677</v>
       </c>
     </row>
     <row r="120">
@@ -96337,17 +96337,17 @@
       </c>
       <c r="IZ120" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>1</v>
+        <v>0.04737674444913864</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC120" t="n">
-        <v>0</v>
+        <v>1.223621924104377</v>
       </c>
     </row>
     <row r="121">
@@ -97132,17 +97132,17 @@
       </c>
       <c r="IZ121" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>1</v>
+        <v>0.04566311091184616</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC121" t="n">
-        <v>0</v>
+        <v>1.223621965617292</v>
       </c>
     </row>
     <row r="122">
@@ -97927,17 +97927,17 @@
       </c>
       <c r="IZ122" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>1</v>
+        <v>0.04453717917203903</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.3999999999999999</v>
       </c>
       <c r="JC122" t="n">
-        <v>0</v>
+        <v>1.223621778809173</v>
       </c>
     </row>
     <row r="123">
@@ -98722,17 +98722,17 @@
       </c>
       <c r="IZ123" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>1</v>
+        <v>0.04323042184114456</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC123" t="n">
-        <v>0</v>
+        <v>1.223621847997365</v>
       </c>
     </row>
     <row r="124">
@@ -99517,17 +99517,17 @@
       </c>
       <c r="IZ124" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>1</v>
+        <v>0.04260637611150742</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC124" t="n">
-        <v>0</v>
+        <v>1.223621647351608</v>
       </c>
     </row>
     <row r="125">
@@ -100312,17 +100312,17 @@
       </c>
       <c r="IZ125" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>1</v>
+        <v>0.04169940203428268</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999996</v>
       </c>
       <c r="JC125" t="n">
-        <v>0</v>
+        <v>1.223621688864523</v>
       </c>
     </row>
     <row r="126">
@@ -101103,21 +101103,21 @@
         <v>0</v>
       </c>
       <c r="IY126" t="n">
-        <v>0</v>
+        <v>-3.873712549958921e-06</v>
       </c>
       <c r="IZ126" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell (Force)</t>
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>1</v>
+        <v>0.04258925467729568</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999996</v>
       </c>
       <c r="JC126" t="n">
-        <v>0</v>
+        <v>1.2236217165398</v>
       </c>
     </row>
   </sheetData>
